--- a/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109D2BB-C761-8A40-A5F3-DFC70BE53348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84835AAA-03A7-D448-8BA8-8E25F835505B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,9 +15,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="151">
-  <si>
-    <t>Supplier quality hold register, Nordvik Manufacturing quality engineering; extract as of October 7, 2026, holds opened since April 2025</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="135">
+  <si>
+    <t>Supplier quality hold register, Nordvik Manufacturing quality engineering; extract as of October 7, 2026, holds opened since September 2025</t>
   </si>
   <si>
     <t>HOLD_NO</t>
@@ -47,372 +47,309 @@
     <t>NOTE</t>
   </si>
   <si>
-    <t>QH-25-011</t>
+    <t>QH-25-022</t>
+  </si>
+  <si>
+    <t>Dalgaard Bearing Co.</t>
+  </si>
+  <si>
+    <t>Deep groove ball bearings 6205</t>
+  </si>
+  <si>
+    <t>09/16/2025</t>
+  </si>
+  <si>
+    <t>Radial play outside C3 on 6 of 20 sampled</t>
+  </si>
+  <si>
+    <t>Cleared</t>
+  </si>
+  <si>
+    <t>10/21/2025</t>
+  </si>
+  <si>
+    <t>M. Quist</t>
+  </si>
+  <si>
+    <t>QH-25-024</t>
+  </si>
+  <si>
+    <t>Halvard Corrugated</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 30 x 20 x 16</t>
+  </si>
+  <si>
+    <t>10/08/2025</t>
+  </si>
+  <si>
+    <t>Glue tab separation on 3 of 40 sampled, lot H-2263</t>
+  </si>
+  <si>
+    <t>11/04/2025</t>
+  </si>
+  <si>
+    <t>R. Aasen</t>
+  </si>
+  <si>
+    <t>QH-25-027</t>
+  </si>
+  <si>
+    <t>Sauk Centre Foam Products</t>
+  </si>
+  <si>
+    <t>Polyethylene foam inserts</t>
+  </si>
+  <si>
+    <t>11/12/2025</t>
+  </si>
+  <si>
+    <t>Density 1.7 pcf against 2.2 pcf specified</t>
+  </si>
+  <si>
+    <t>12/16/2025</t>
+  </si>
+  <si>
+    <t>T. Bjornstad</t>
+  </si>
+  <si>
+    <t>QH-26-002</t>
+  </si>
+  <si>
+    <t>Northfield Gasket</t>
+  </si>
+  <si>
+    <t>Neoprene gaskets, pump housing</t>
+  </si>
+  <si>
+    <t>01/13/2026</t>
+  </si>
+  <si>
+    <t>Durometer 68 against 60 plus or minus 5</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>QH-26-004</t>
+  </si>
+  <si>
+    <t>Bemidji Wire Forms</t>
+  </si>
+  <si>
+    <t>Formed wire hangers</t>
+  </si>
+  <si>
+    <t>01/27/2026</t>
+  </si>
+  <si>
+    <t>Weld spatter on 12 of 50 sampled</t>
+  </si>
+  <si>
+    <t>02/24/2026</t>
+  </si>
+  <si>
+    <t>QH-26-006</t>
+  </si>
+  <si>
+    <t>Thief River Plastics</t>
+  </si>
+  <si>
+    <t>Injection molded end caps</t>
+  </si>
+  <si>
+    <t>02/17/2026</t>
+  </si>
+  <si>
+    <t>Short shots on cavity 4, lot TR-0312</t>
+  </si>
+  <si>
+    <t>03/17/2026</t>
+  </si>
+  <si>
+    <t>QH-26-009</t>
+  </si>
+  <si>
+    <t>Pemberton Container</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 24 x 18 x 12</t>
+  </si>
+  <si>
+    <t>03/04/2026</t>
+  </si>
+  <si>
+    <t>Flap scoring cracked on 8 of 40 sampled, lot P-26-0407</t>
+  </si>
+  <si>
+    <t>05/12/2026</t>
+  </si>
+  <si>
+    <t>Scoring rule replaced at the Neenah plant; verification lot passed</t>
+  </si>
+  <si>
+    <t>QH-26-012</t>
+  </si>
+  <si>
+    <t>Crookston Steel Service</t>
+  </si>
+  <si>
+    <t>Hot rolled plate, 3/8 inch</t>
+  </si>
+  <si>
+    <t>03/26/2026</t>
+  </si>
+  <si>
+    <t>Mill cert missing for heat 44189</t>
+  </si>
+  <si>
+    <t>04/02/2026</t>
+  </si>
+  <si>
+    <t>QH-26-013</t>
+  </si>
+  <si>
+    <t>Wadena Powder Coating</t>
+  </si>
+  <si>
+    <t>Powder coat, RAL 7035</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>Film thickness 1.6 mil against 2.0 to 3.0 mil</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>QH-26-016</t>
+  </si>
+  <si>
+    <t>Detroit Lakes Printing</t>
+  </si>
+  <si>
+    <t>Instruction sheets, folded</t>
+  </si>
+  <si>
+    <t>04/28/2026</t>
+  </si>
+  <si>
+    <t>Wrong revision printed, rev C shipped against rev D</t>
+  </si>
+  <si>
+    <t>05/19/2026</t>
+  </si>
+  <si>
+    <t>QH-26-018</t>
+  </si>
+  <si>
+    <t>Mille Lacs Motor Repair</t>
+  </si>
+  <si>
+    <t>Rewound gearmotors</t>
+  </si>
+  <si>
+    <t>05/13/2026</t>
+  </si>
+  <si>
+    <t>Insulation resistance under 100 megohm on 2 of 6</t>
+  </si>
+  <si>
+    <t>06/23/2026</t>
+  </si>
+  <si>
+    <t>QH-26-021</t>
   </si>
   <si>
     <t>Kittson Fastener Supply</t>
   </si>
   <si>
-    <t>Hex bolts, grade 8</t>
-  </si>
-  <si>
-    <t>04/14/2025</t>
-  </si>
-  <si>
-    <t>Plating thickness under 8 microns on lot K-4471</t>
-  </si>
-  <si>
-    <t>Cleared</t>
-  </si>
-  <si>
-    <t>05/06/2025</t>
-  </si>
-  <si>
-    <t>M. Quist</t>
-  </si>
-  <si>
-    <t>QH-25-014</t>
+    <t>Flange nuts, M10</t>
+  </si>
+  <si>
+    <t>06/02/2026</t>
+  </si>
+  <si>
+    <t>Thread gauge no-go accepted on 4 of 100 sampled</t>
+  </si>
+  <si>
+    <t>06/30/2026</t>
+  </si>
+  <si>
+    <t>QH-26-023</t>
+  </si>
+  <si>
+    <t>Prairie Resin &amp; Compound</t>
+  </si>
+  <si>
+    <t>Polypropylene, black</t>
+  </si>
+  <si>
+    <t>06/24/2026</t>
+  </si>
+  <si>
+    <t>Contamination specks visible in molded parts</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>QH-26-025</t>
+  </si>
+  <si>
+    <t>Vermilion Label Works</t>
+  </si>
+  <si>
+    <t>Barcode labels, 2 x 1</t>
+  </si>
+  <si>
+    <t>07/15/2026</t>
+  </si>
+  <si>
+    <t>Grade C scan on 3 rolls, lot V-8827</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>QH-26-027</t>
+  </si>
+  <si>
+    <t>Loken Bros. Pallet &amp; Crate</t>
+  </si>
+  <si>
+    <t>Pallets, 48 x 40 hardwood</t>
+  </si>
+  <si>
+    <t>07/30/2026</t>
+  </si>
+  <si>
+    <t>Board moisture over 19 percent on the July delivery</t>
+  </si>
+  <si>
+    <t>QH-26-028</t>
+  </si>
+  <si>
+    <t>Cork rubber gaskets</t>
+  </si>
+  <si>
+    <t>08/06/2026</t>
+  </si>
+  <si>
+    <t>Sheet thickness 1/16 shipped against 1/8 ordered</t>
+  </si>
+  <si>
+    <t>08/13/2026</t>
+  </si>
+  <si>
+    <t>QH-26-031</t>
   </si>
   <si>
     <t>Loken &amp; Vik Container Corp.</t>
   </si>
   <si>
-    <t>Corrugated, retail display trays</t>
-  </si>
-  <si>
-    <t>06/11/2025</t>
-  </si>
-  <si>
-    <t>Print registration out of tolerance on lot 25-1187</t>
-  </si>
-  <si>
-    <t>07/02/2025</t>
-  </si>
-  <si>
-    <t>R. Aasen</t>
-  </si>
-  <si>
-    <t>QH-25-017</t>
-  </si>
-  <si>
-    <t>Prairie Resin &amp; Compound</t>
-  </si>
-  <si>
-    <t>Polypropylene, natural</t>
-  </si>
-  <si>
-    <t>07/22/2025</t>
-  </si>
-  <si>
-    <t>Melt flow 14 against 11 to 13 specified, drum lot 7719</t>
-  </si>
-  <si>
-    <t>08/19/2025</t>
-  </si>
-  <si>
-    <t>T. Bjornstad</t>
-  </si>
-  <si>
-    <t>QH-25-019</t>
-  </si>
-  <si>
-    <t>Vermilion Label Works</t>
-  </si>
-  <si>
-    <t>Pressure sensitive labels, 4 x 6</t>
-  </si>
-  <si>
-    <t>08/05/2025</t>
-  </si>
-  <si>
-    <t>Adhesive lifting at 40 F in cold room trial</t>
-  </si>
-  <si>
-    <t>09/30/2025</t>
-  </si>
-  <si>
-    <t>Adhesive changed to the freezer grade</t>
-  </si>
-  <si>
-    <t>QH-25-022</t>
-  </si>
-  <si>
-    <t>Dalgaard Bearing Co.</t>
-  </si>
-  <si>
-    <t>Deep groove ball bearings 6205</t>
-  </si>
-  <si>
-    <t>09/16/2025</t>
-  </si>
-  <si>
-    <t>Radial play outside C3 on 6 of 20 sampled</t>
-  </si>
-  <si>
-    <t>10/21/2025</t>
-  </si>
-  <si>
-    <t>QH-25-024</t>
-  </si>
-  <si>
-    <t>Halvard Corrugated</t>
-  </si>
-  <si>
-    <t>Corrugated, RSC 30 x 20 x 16</t>
-  </si>
-  <si>
-    <t>10/08/2025</t>
-  </si>
-  <si>
-    <t>Glue tab separation on 3 of 40 sampled, lot H-2263</t>
-  </si>
-  <si>
-    <t>11/04/2025</t>
-  </si>
-  <si>
-    <t>QH-25-027</t>
-  </si>
-  <si>
-    <t>Sauk Centre Foam Products</t>
-  </si>
-  <si>
-    <t>Polyethylene foam inserts</t>
-  </si>
-  <si>
-    <t>11/12/2025</t>
-  </si>
-  <si>
-    <t>Density 1.7 pcf against 2.2 pcf specified</t>
-  </si>
-  <si>
-    <t>12/16/2025</t>
-  </si>
-  <si>
-    <t>QH-26-002</t>
-  </si>
-  <si>
-    <t>Northfield Gasket</t>
-  </si>
-  <si>
-    <t>Neoprene gaskets, pump housing</t>
-  </si>
-  <si>
-    <t>01/13/2026</t>
-  </si>
-  <si>
-    <t>Durometer 68 against 60 plus or minus 5</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>QH-26-004</t>
-  </si>
-  <si>
-    <t>Bemidji Wire Forms</t>
-  </si>
-  <si>
-    <t>Formed wire hangers</t>
-  </si>
-  <si>
-    <t>01/27/2026</t>
-  </si>
-  <si>
-    <t>Weld spatter on 12 of 50 sampled</t>
-  </si>
-  <si>
-    <t>02/24/2026</t>
-  </si>
-  <si>
-    <t>QH-26-006</t>
-  </si>
-  <si>
-    <t>Thief River Plastics</t>
-  </si>
-  <si>
-    <t>Injection molded end caps</t>
-  </si>
-  <si>
-    <t>02/17/2026</t>
-  </si>
-  <si>
-    <t>Short shots on cavity 4, lot TR-0312</t>
-  </si>
-  <si>
-    <t>03/17/2026</t>
-  </si>
-  <si>
-    <t>QH-26-009</t>
-  </si>
-  <si>
-    <t>Pemberton Container</t>
-  </si>
-  <si>
-    <t>Corrugated, RSC 24 x 18 x 12</t>
-  </si>
-  <si>
-    <t>03/04/2026</t>
-  </si>
-  <si>
-    <t>Flap scoring cracked on 8 of 40 sampled, lot P-26-0407</t>
-  </si>
-  <si>
-    <t>05/12/2026</t>
-  </si>
-  <si>
-    <t>Scoring rule replaced at the Neenah plant; verification lot passed</t>
-  </si>
-  <si>
-    <t>QH-26-012</t>
-  </si>
-  <si>
-    <t>Crookston Steel Service</t>
-  </si>
-  <si>
-    <t>Hot rolled plate, 3/8 inch</t>
-  </si>
-  <si>
-    <t>03/26/2026</t>
-  </si>
-  <si>
-    <t>Mill cert missing for heat 44189</t>
-  </si>
-  <si>
-    <t>04/02/2026</t>
-  </si>
-  <si>
-    <t>QH-26-013</t>
-  </si>
-  <si>
-    <t>Wadena Powder Coating</t>
-  </si>
-  <si>
-    <t>Powder coat, RAL 7035</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>Film thickness 1.6 mil against 2.0 to 3.0 mil</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
-  </si>
-  <si>
-    <t>QH-26-016</t>
-  </si>
-  <si>
-    <t>Detroit Lakes Printing</t>
-  </si>
-  <si>
-    <t>Instruction sheets, folded</t>
-  </si>
-  <si>
-    <t>04/28/2026</t>
-  </si>
-  <si>
-    <t>Wrong revision printed, rev C shipped against rev D</t>
-  </si>
-  <si>
-    <t>05/19/2026</t>
-  </si>
-  <si>
-    <t>QH-26-018</t>
-  </si>
-  <si>
-    <t>Mille Lacs Motor Repair</t>
-  </si>
-  <si>
-    <t>Rewound gearmotors</t>
-  </si>
-  <si>
-    <t>05/13/2026</t>
-  </si>
-  <si>
-    <t>Insulation resistance under 100 megohm on 2 of 6</t>
-  </si>
-  <si>
-    <t>06/23/2026</t>
-  </si>
-  <si>
-    <t>QH-26-021</t>
-  </si>
-  <si>
-    <t>Flange nuts, M10</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
-    <t>Thread gauge no-go accepted on 4 of 100 sampled</t>
-  </si>
-  <si>
-    <t>06/30/2026</t>
-  </si>
-  <si>
-    <t>QH-26-023</t>
-  </si>
-  <si>
-    <t>Polypropylene, black</t>
-  </si>
-  <si>
-    <t>06/24/2026</t>
-  </si>
-  <si>
-    <t>Contamination specks visible in molded parts</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>QH-26-025</t>
-  </si>
-  <si>
-    <t>Barcode labels, 2 x 1</t>
-  </si>
-  <si>
-    <t>07/15/2026</t>
-  </si>
-  <si>
-    <t>Grade C scan on 3 rolls, lot V-8827</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>QH-26-027</t>
-  </si>
-  <si>
-    <t>Loken Bros. Pallet &amp; Crate</t>
-  </si>
-  <si>
-    <t>Pallets, 48 x 40 hardwood</t>
-  </si>
-  <si>
-    <t>07/30/2026</t>
-  </si>
-  <si>
-    <t>Board moisture over 19 percent on the July delivery</t>
-  </si>
-  <si>
-    <t>QH-26-028</t>
-  </si>
-  <si>
-    <t>Cork rubber gaskets</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Sheet thickness 1/16 shipped against 1/8 ordered</t>
-  </si>
-  <si>
-    <t>08/13/2026</t>
-  </si>
-  <si>
-    <t>QH-26-031</t>
-  </si>
-  <si>
     <t>Corrugated, RSC 16 x 12 x 8</t>
   </si>
   <si>
@@ -435,6 +372,21 @@
   </si>
   <si>
     <t>09/22/2026</t>
+  </si>
+  <si>
+    <t>QH-26-034</t>
+  </si>
+  <si>
+    <t>Pemberton Container, Neenah plant</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>Board caliper 0.148 inch against 0.156 inch minimum on lot P-26-0902</t>
+  </si>
+  <si>
+    <t>Verification lot due from Neenah the week of 10/12/2026</t>
   </si>
   <si>
     <t>QH-26-035</t>
@@ -846,7 +798,7 @@
     <col min="9" max="9" width="60" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -984,92 +936,92 @@
         <v>37</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>38</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I7" s="3"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="I9" s="3"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -1121,7 +1073,7 @@
         <v>68</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I12" s="3"/>
     </row>
@@ -1148,7 +1100,7 @@
         <v>74</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3"/>
     </row>
@@ -1175,33 +1127,31 @@
         <v>80</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>81</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>17</v>
@@ -1210,80 +1160,76 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>92</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>99</v>
-      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I17" s="3"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>104</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>105</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
         <v>17</v>
       </c>
@@ -1291,25 +1237,25 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>15</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>17</v>
@@ -1318,241 +1264,197 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="F21" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="3"/>
+        <v>24</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>130</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>135</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I25" s="3"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
+      <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>120</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
       <c r="G27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>120</v>
-      </c>
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
       <c r="G28" s="3"/>
-      <c r="H28" s="3" t="s">
-        <v>24</v>
-      </c>
+      <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>150</v>
-      </c>
+      <c r="A30" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84835AAA-03A7-D448-8BA8-8E25F835505B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0193F1-F99C-074F-8208-528349FA78EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="152">
   <si>
     <t>Supplier quality hold register, Nordvik Manufacturing quality engineering; extract as of October 7, 2026, holds opened since September 2025</t>
   </si>
@@ -47,6 +47,9 @@
     <t>NOTE</t>
   </si>
   <si>
+    <t>SUPPLIER_ADDRESS</t>
+  </si>
+  <si>
     <t>QH-25-022</t>
   </si>
   <si>
@@ -71,6 +74,9 @@
     <t>M. Quist</t>
   </si>
   <si>
+    <t>1410 Industrial Road, Grand Forks, ND</t>
+  </si>
+  <si>
     <t>QH-25-024</t>
   </si>
   <si>
@@ -92,6 +98,9 @@
     <t>R. Aasen</t>
   </si>
   <si>
+    <t>3811 12th Avenue North, Fargo, ND</t>
+  </si>
+  <si>
     <t>QH-25-027</t>
   </si>
   <si>
@@ -113,6 +122,9 @@
     <t>T. Bjornstad</t>
   </si>
   <si>
+    <t>2200 Main Street South, Sauk Centre, MN</t>
+  </si>
+  <si>
     <t>QH-26-002</t>
   </si>
   <si>
@@ -131,6 +143,9 @@
     <t>02/10/2026</t>
   </si>
   <si>
+    <t>900 Riverview Drive, Northfield, MN</t>
+  </si>
+  <si>
     <t>QH-26-004</t>
   </si>
   <si>
@@ -149,6 +164,9 @@
     <t>02/24/2026</t>
   </si>
   <si>
+    <t>1750 Paul Bunyan Drive, Bemidji, MN</t>
+  </si>
+  <si>
     <t>QH-26-006</t>
   </si>
   <si>
@@ -167,6 +185,9 @@
     <t>03/17/2026</t>
   </si>
   <si>
+    <t>315 Pennington Avenue, Thief River Falls, MN</t>
+  </si>
+  <si>
     <t>QH-26-009</t>
   </si>
   <si>
@@ -188,6 +209,9 @@
     <t>Scoring rule replaced at the Neenah plant; verification lot passed</t>
   </si>
   <si>
+    <t>900 Industrial Drive, Neenah, WI</t>
+  </si>
+  <si>
     <t>QH-26-012</t>
   </si>
   <si>
@@ -206,6 +230,9 @@
     <t>04/02/2026</t>
   </si>
   <si>
+    <t>1100 Robert Street, Crookston, MN</t>
+  </si>
+  <si>
     <t>QH-26-013</t>
   </si>
   <si>
@@ -224,6 +251,9 @@
     <t>05/05/2026</t>
   </si>
   <si>
+    <t>612 Aldrich Avenue, Wadena, MN</t>
+  </si>
+  <si>
     <t>QH-26-016</t>
   </si>
   <si>
@@ -242,6 +272,9 @@
     <t>05/19/2026</t>
   </si>
   <si>
+    <t>1215 Washington Avenue, Detroit Lakes, MN</t>
+  </si>
+  <si>
     <t>QH-26-018</t>
   </si>
   <si>
@@ -260,6 +293,9 @@
     <t>06/23/2026</t>
   </si>
   <si>
+    <t>28 Fourth Street, Onamia, MN</t>
+  </si>
+  <si>
     <t>QH-26-021</t>
   </si>
   <si>
@@ -278,6 +314,9 @@
     <t>06/30/2026</t>
   </si>
   <si>
+    <t>501 Atlantic Avenue, Hallock, MN</t>
+  </si>
+  <si>
     <t>QH-26-023</t>
   </si>
   <si>
@@ -296,6 +335,9 @@
     <t>08/04/2026</t>
   </si>
   <si>
+    <t>4400 Highway 10 West, Moorhead, MN</t>
+  </si>
+  <si>
     <t>QH-26-025</t>
   </si>
   <si>
@@ -314,19 +356,25 @@
     <t>Open</t>
   </si>
   <si>
+    <t>77 Lake Street, Tower, MN</t>
+  </si>
+  <si>
     <t>QH-26-027</t>
   </si>
   <si>
-    <t>Loken Bros. Pallet &amp; Crate</t>
-  </si>
-  <si>
-    <t>Pallets, 48 x 40 hardwood</t>
+    <t>Loken Container Supply, Sioux City</t>
+  </si>
+  <si>
+    <t>Corrugated, RSC 30 x 24 x 18</t>
   </si>
   <si>
     <t>07/30/2026</t>
   </si>
   <si>
-    <t>Board moisture over 19 percent on the July delivery</t>
+    <t>Flute crush on 4 of 20 sampled, July delivery</t>
+  </si>
+  <si>
+    <t>2100 Dace Avenue, Sioux City, IA</t>
   </si>
   <si>
     <t>QH-26-028</t>
@@ -347,7 +395,7 @@
     <t>QH-26-031</t>
   </si>
   <si>
-    <t>Loken &amp; Vik Container Corp.</t>
+    <t>L&amp;V Container Corp., Sioux Falls</t>
   </si>
   <si>
     <t>Corrugated, RSC 16 x 12 x 8</t>
@@ -360,6 +408,9 @@
   </si>
   <si>
     <t>Corrective action received 09/18/2026; verification lot not yet run</t>
+  </si>
+  <si>
+    <t>4700 North Cliff Avenue, Sioux Falls, SD</t>
   </si>
   <si>
     <t>QH-26-033</t>
@@ -426,7 +477,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +493,12 @@
     <font>
       <b/>
       <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -477,11 +534,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -784,7 +842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -796,14 +854,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="10" max="10" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -831,594 +890,663 @@
       <c r="I3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="3"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="3"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="I7" s="3"/>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="3"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="I12" s="3"/>
+      <c r="J12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="3"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="3"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="3"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="I13" s="3"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J16" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>130</v>
+      </c>
+      <c r="J20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+      <c r="J22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J23" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J24" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J25" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1429,9 +1557,9 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1442,7 +1570,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1453,7 +1581,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
     </row>
   </sheetData>

--- a/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
+++ b/submissions/10-carton-bid-evaluation/inputs/supplier_quality_holds_2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0193F1-F99C-074F-8208-528349FA78EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8213D7BA-C5C7-544D-AA51-ED6A3A3078A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="38400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="153">
   <si>
     <t>Supplier quality hold register, Nordvik Manufacturing quality engineering; extract as of October 7, 2026, holds opened since September 2025</t>
   </si>
@@ -377,19 +377,22 @@
     <t>2100 Dace Avenue, Sioux City, IA</t>
   </si>
   <si>
-    <t>QH-26-028</t>
-  </si>
-  <si>
-    <t>Cork rubber gaskets</t>
-  </si>
-  <si>
-    <t>08/06/2026</t>
-  </si>
-  <si>
-    <t>Sheet thickness 1/16 shipped against 1/8 ordered</t>
-  </si>
-  <si>
-    <t>08/13/2026</t>
+    <t>QH-26-029</t>
+  </si>
+  <si>
+    <t>Pemberton Fibre Products, Green Bay</t>
+  </si>
+  <si>
+    <t>08/19/2026</t>
+  </si>
+  <si>
+    <t>Print registration out of tolerance on lot G-26-0811</t>
+  </si>
+  <si>
+    <t>Verification lot G-26-1004 due from Green Bay the week of 10/19/2026</t>
+  </si>
+  <si>
+    <t>1200 Lime Kiln Road, Green Bay, WI</t>
   </si>
   <si>
     <t>QH-26-031</t>
@@ -437,7 +440,7 @@
     <t>Board caliper 0.148 inch against 0.156 inch minimum on lot P-26-0902</t>
   </si>
   <si>
-    <t>Verification lot due from Neenah the week of 10/12/2026</t>
+    <t>Verification lot P-26-1009 due from Neenah the week of 10/12/2026</t>
   </si>
   <si>
     <t>QH-26-035</t>
@@ -1347,10 +1350,10 @@
         <v>120</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>121</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>122</v>
@@ -1359,34 +1362,34 @@
         <v>123</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="3"/>
       <c r="J19" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>112</v>
@@ -1396,15 +1399,15 @@
         <v>26</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>29</v>
@@ -1413,16 +1416,16 @@
         <v>30</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>16</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>34</v>
@@ -1434,19 +1437,19 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>112</v>
@@ -1456,7 +1459,7 @@
         <v>26</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J22" t="s">
         <v>64</v>
@@ -1464,7 +1467,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>44</v>
@@ -1473,10 +1476,10 @@
         <v>45</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>112</v>
@@ -1492,19 +1495,19 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>112</v>
@@ -1520,7 +1523,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>51</v>
@@ -1529,10 +1532,10 @@
         <v>52</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>112</v>
@@ -1559,7 +1562,7 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
